--- a/denodo_agent_poc/data/results/consolidated_dq_insights.xlsx
+++ b/denodo_agent_poc/data/results/consolidated_dq_insights.xlsx
@@ -468,7 +468,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-28T12:26:19.079891+00:00</t>
+          <t>2026-07-29T05:57:07.131399+00:00</t>
         </is>
       </c>
       <c r="B2" t="n">
